--- a/Additional Helping Files/marks/marks-106.xlsx
+++ b/Additional Helping Files/marks/marks-106.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TechnicalHouse\Additional Helping Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TechnicalHouse\Additional Helping Files\marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99AB8C5-4577-4325-A105-619C9E7CA1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9200D24C-D4A8-47C8-8236-F00478EA20BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -174,9 +174,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -459,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="18" defaultRowHeight="30.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="18" style="1"/>
@@ -469,7 +466,7 @@
     <col min="10" max="16384" width="18" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -509,9 +506,8 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -536,15 +532,24 @@
       <c r="H2" s="1">
         <v>5</v>
       </c>
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10</v>
+      </c>
       <c r="L2" s="1">
         <v>20</v>
       </c>
       <c r="M2" s="1">
         <f>SUM(B2:L2)</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
@@ -569,15 +574,24 @@
       <c r="H3" s="1">
         <v>5</v>
       </c>
+      <c r="I3" s="1">
+        <v>8</v>
+      </c>
+      <c r="J3" s="1">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>8</v>
+      </c>
       <c r="L3" s="1">
         <v>20</v>
       </c>
       <c r="M3" s="1">
         <f>SUM(B3:L3)</f>
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -602,15 +616,24 @@
       <c r="H4" s="1">
         <v>3</v>
       </c>
+      <c r="I4" s="1">
+        <v>7</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1">
+        <v>7</v>
+      </c>
       <c r="L4" s="1">
         <v>20</v>
       </c>
       <c r="M4" s="1">
         <f>SUM(B4:L4)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -635,15 +658,24 @@
       <c r="H5" s="1">
         <v>0</v>
       </c>
+      <c r="I5" s="1">
+        <v>8</v>
+      </c>
+      <c r="J5" s="1">
+        <v>8</v>
+      </c>
+      <c r="K5" s="1">
+        <v>7</v>
+      </c>
       <c r="L5" s="1">
         <v>19</v>
       </c>
       <c r="M5" s="1">
         <f>SUM(B5:L5)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -668,48 +700,66 @@
       <c r="H6" s="1">
         <v>2</v>
       </c>
+      <c r="I6" s="1">
+        <v>4</v>
+      </c>
+      <c r="J6" s="1">
+        <v>7</v>
+      </c>
+      <c r="K6" s="1">
+        <v>5</v>
+      </c>
       <c r="L6" s="1">
         <v>19</v>
       </c>
       <c r="M6" s="1">
         <f>SUM(B6:L6)</f>
-        <v>58.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1">
+        <v>7</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>7</v>
+      </c>
+      <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="1">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="F7" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2.5</v>
+      <c r="K7" s="1">
+        <v>6</v>
       </c>
       <c r="L7" s="1">
         <v>18.5</v>
       </c>
       <c r="M7" s="1">
         <f>SUM(B7:L7)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -734,48 +784,66 @@
       <c r="H8" s="1">
         <v>3</v>
       </c>
+      <c r="I8" s="1">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3</v>
+      </c>
       <c r="L8" s="1">
         <v>18.5</v>
       </c>
       <c r="M8" s="1">
         <f>SUM(B8:L8)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F9" s="1">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G9" s="1">
         <v>5</v>
       </c>
       <c r="H9" s="1">
-        <v>3</v>
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>5</v>
       </c>
       <c r="L9" s="1">
         <v>18.5</v>
       </c>
       <c r="M9" s="1">
         <f>SUM(B9:L9)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -800,15 +868,24 @@
       <c r="H10" s="1">
         <v>0</v>
       </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6</v>
+      </c>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
       <c r="L10" s="1">
         <v>16.5</v>
       </c>
       <c r="M10" s="1">
         <f>SUM(B10:L10)</f>
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -833,12 +910,21 @@
       <c r="H11" s="1">
         <v>0.5</v>
       </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>6</v>
+      </c>
+      <c r="K11" s="1">
+        <v>7</v>
+      </c>
       <c r="L11" s="1">
         <v>17</v>
       </c>
       <c r="M11" s="1">
         <f>SUM(B11:L11)</f>
-        <v>41.5</v>
+        <v>60.5</v>
       </c>
     </row>
   </sheetData>
